--- a/sample/orders.xlsx
+++ b/sample/orders.xlsx
@@ -1376,7 +1376,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sep 15, 2026</t>
+          <t xml:space="preserve">Oct 05, 2026</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sep 15, 2026</t>
+          <t xml:space="preserve">Sep 18, 2026</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sep 16, 2026</t>
+          <t xml:space="preserve">Jan 20, 2027</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sep 16, 2026</t>
+          <t xml:space="preserve">Nov 20, 2026</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sep 17, 2026</t>
+          <t xml:space="preserve">Apr 12, 2027</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1852,11 +1852,6 @@
       <c r="T7" t="inlineStr">
         <is>
           <t xml:space="preserve">Happy birthday!! </t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sep 17, 2026</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">

--- a/sample/orders.xlsx
+++ b/sample/orders.xlsx
@@ -1583,7 +1583,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sra. Pena</t>
+          <t xml:space="preserve">Sra. Peña</t>
         </is>
       </c>
     </row>
